--- a/survey_results.xlsx
+++ b/survey_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY2"/>
+  <dimension ref="A1:CY1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -942,445 +942,6 @@
       <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>Q25_axis</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>17654</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>احمد مازن عدنان الخانجي</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>الأولية المختلطة / جبل عمان</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>الأب</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>ddddddd</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>dddd</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ddd</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="K2" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-03-23 15:48:04</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>المحور الأول: البيئة المدرسية</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P2" t="n">
-        <v>68</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>المحور الثاني: المستوى الأكاديمي</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="S2" t="n">
-        <v>76</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>المحور الثالث: المعلمون</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V2" t="n">
-        <v>76</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>المحور الرابع: التواصل مع ولي الأمر</t>
-        </is>
-      </c>
-      <c r="X2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>96</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>المحور الخامس: الرضا العام</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>76</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>هل تشعر أن المدرسة توفر بيئة آمنة لابنك/ابنتك؟</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>المحور الأول: البيئة المدرسية</t>
-        </is>
-      </c>
-      <c r="AF2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>هل المدرسة نظيفة ومرتبة بشكل مناسب؟</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>المحور الأول: البيئة المدرسية</t>
-        </is>
-      </c>
-      <c r="AI2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>هل يتم الاهتمام براحة الطلبة داخل المدرسة؟</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>المحور الأول: البيئة المدرسية</t>
-        </is>
-      </c>
-      <c r="AL2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>هل المدرسة تتواصل بوضوح عند وجود ملاحظات؟</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>المحور الأول: البيئة المدرسية</t>
-        </is>
-      </c>
-      <c r="AO2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>هل ترى أن مرافق المدرسة مناسبة للطلبة؟</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>المحور الأول: البيئة المدرسية</t>
-        </is>
-      </c>
-      <c r="AR2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>هل مستوى التدريس مناسب لابنك/ابنتك؟</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>المحور الثاني: المستوى الأكاديمي</t>
-        </is>
-      </c>
-      <c r="AU2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>هل الواجبات المنزلية مناسبة من حيث الكم والمحتوى؟</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>المحور الثاني: المستوى الأكاديمي</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>هل يتم متابعة تقدم الطالب بشكل مستمر؟</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>المحور الثاني: المستوى الأكاديمي</t>
-        </is>
-      </c>
-      <c r="BA2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>هل تشعر بوجود تحسن في المستوى الدراسي؟</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>المحور الثاني: المستوى الأكاديمي</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>هل الشرح داخل الصف واضح ومفيد؟</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>المحور الثاني: المستوى الأكاديمي</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>هل المعلمون يتعاملون باحترام مع الطلبة؟</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>المحور الثالث: المعلمون</t>
-        </is>
-      </c>
-      <c r="BJ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>هل المعلمون متعاونون مع أولياء الأمور؟</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>المحور الثالث: المعلمون</t>
-        </is>
-      </c>
-      <c r="BM2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>هل يوضح المعلمون نقاط القوة والضعف للطالب؟</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>المحور الثالث: المعلمون</t>
-        </is>
-      </c>
-      <c r="BP2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>هل المعلمون يراعون الفروق الفردية بين الطلبة؟</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>المحور الثالث: المعلمون</t>
-        </is>
-      </c>
-      <c r="BS2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>هل ترى أن المعلمين ملتزمون بمهامهم؟</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>المحور الثالث: المعلمون</t>
-        </is>
-      </c>
-      <c r="BV2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>هل إدارة المدرسة تتواصل معك بشكل كافٍ؟</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>المحور الرابع: التواصل مع ولي الأمر</t>
-        </is>
-      </c>
-      <c r="BY2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>هل تستقبل الملاحظات الأكاديمية والسلوكية بانتظام؟</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>المحور الرابع: التواصل مع ولي الأمر</t>
-        </is>
-      </c>
-      <c r="CB2" t="n">
-        <v>4</v>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>هل المدرسة تستجيب لاستفساراتك بسرعة؟</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>المحور الرابع: التواصل مع ولي الأمر</t>
-        </is>
-      </c>
-      <c r="CE2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>هل قنوات التواصل مع المدرسة فعالة؟</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>المحور الرابع: التواصل مع ولي الأمر</t>
-        </is>
-      </c>
-      <c r="CH2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CI2" t="inlineStr">
-        <is>
-          <t>هل تشعر أن رأيك كولي أمر محل اهتمام؟</t>
-        </is>
-      </c>
-      <c r="CJ2" t="inlineStr">
-        <is>
-          <t>المحور الرابع: التواصل مع ولي الأمر</t>
-        </is>
-      </c>
-      <c r="CK2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CL2" t="inlineStr">
-        <is>
-          <t>هل أنت راضٍ بشكل عام عن المدرسة؟</t>
-        </is>
-      </c>
-      <c r="CM2" t="inlineStr">
-        <is>
-          <t>المحور الخامس: الرضا العام</t>
-        </is>
-      </c>
-      <c r="CN2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CO2" t="inlineStr">
-        <is>
-          <t>هل تنصح أولياء الأمور الآخرين بهذه المدرسة؟</t>
-        </is>
-      </c>
-      <c r="CP2" t="inlineStr">
-        <is>
-          <t>المحور الخامس: الرضا العام</t>
-        </is>
-      </c>
-      <c r="CQ2" t="n">
-        <v>5</v>
-      </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>هل تعتقد أن المدرسة تلبي احتياجات الطالب؟</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>المحور الخامس: الرضا العام</t>
-        </is>
-      </c>
-      <c r="CT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>هل ترى أن مستوى الانضباط في المدرسة جيد؟</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>المحور الخامس: الرضا العام</t>
-        </is>
-      </c>
-      <c r="CW2" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>هل ترغب في استمرار ابنك/ابنتك في هذه المدرسة؟</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>المحور الخامس: الرضا العام</t>
         </is>
       </c>
     </row>

--- a/survey_results.xlsx
+++ b/survey_results.xlsx
@@ -1,47 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mbasheer\Desktop\Data power bi\survy\Streamlit_app\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5631A765-DE7F-4831-98E0-A772DAD2A6BD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7530" windowHeight="6480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -56,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -380,114 +420,1137 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CY1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:DQ2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:103" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
-      <c r="AL1" s="1"/>
-      <c r="AM1" s="1"/>
-      <c r="AN1" s="1"/>
-      <c r="AO1" s="1"/>
-      <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
-      <c r="AR1" s="1"/>
-      <c r="AS1" s="1"/>
-      <c r="AT1" s="1"/>
-      <c r="AU1" s="1"/>
-      <c r="AV1" s="1"/>
-      <c r="AW1" s="1"/>
-      <c r="AX1" s="1"/>
-      <c r="AY1" s="1"/>
-      <c r="AZ1" s="1"/>
-      <c r="BA1" s="1"/>
-      <c r="BB1" s="1"/>
-      <c r="BC1" s="1"/>
-      <c r="BD1" s="1"/>
-      <c r="BE1" s="1"/>
-      <c r="BF1" s="1"/>
-      <c r="BG1" s="1"/>
-      <c r="BH1" s="1"/>
-      <c r="BI1" s="1"/>
-      <c r="BJ1" s="1"/>
-      <c r="BK1" s="1"/>
-      <c r="BL1" s="1"/>
-      <c r="BM1" s="1"/>
-      <c r="BN1" s="1"/>
-      <c r="BO1" s="1"/>
-      <c r="BP1" s="1"/>
-      <c r="BQ1" s="1"/>
-      <c r="BR1" s="1"/>
-      <c r="BS1" s="1"/>
-      <c r="BT1" s="1"/>
-      <c r="BU1" s="1"/>
-      <c r="BV1" s="1"/>
-      <c r="BW1" s="1"/>
-      <c r="BX1" s="1"/>
-      <c r="BY1" s="1"/>
-      <c r="BZ1" s="1"/>
-      <c r="CA1" s="1"/>
-      <c r="CB1" s="1"/>
-      <c r="CC1" s="1"/>
-      <c r="CD1" s="1"/>
-      <c r="CE1" s="1"/>
-      <c r="CF1" s="1"/>
-      <c r="CG1" s="1"/>
-      <c r="CH1" s="1"/>
-      <c r="CI1" s="1"/>
-      <c r="CJ1" s="1"/>
-      <c r="CK1" s="1"/>
-      <c r="CL1" s="1"/>
-      <c r="CM1" s="1"/>
-      <c r="CN1" s="1"/>
-      <c r="CO1" s="1"/>
-      <c r="CP1" s="1"/>
-      <c r="CQ1" s="1"/>
-      <c r="CR1" s="1"/>
-      <c r="CS1" s="1"/>
-      <c r="CT1" s="1"/>
-      <c r="CU1" s="1"/>
-      <c r="CV1" s="1"/>
-      <c r="CW1" s="1"/>
-      <c r="CX1" s="1"/>
-      <c r="CY1" s="1"/>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>student_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>student_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>school</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>survey_type</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>respondent_type</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>respondent_other</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>father_job</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>mother_job</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>contact_phone</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>transport_subscribed</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>bus_number</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>overall_avg</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>overall_pct</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>axis1_name</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>axis1_avg</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>axis1_pct</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>axis2_name</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>axis2_avg</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>axis2_pct</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>axis3_name</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>axis3_avg</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>axis3_pct</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>axis4_name</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>axis4_avg</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>axis4_pct</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>axis5_name</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>axis5_avg</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>axis5_pct</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>axis6_name</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>axis6_avg</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>axis6_pct</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Q1_text</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Q1_axis</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Q2_text</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Q2_axis</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Q3_text</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>Q3_axis</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Q4_text</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Q4_axis</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Q5_text</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>Q5_axis</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>Q6_text</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>Q6_axis</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>Q7_text</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>Q7_axis</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>Q8_text</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>Q8_axis</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Q9_text</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Q9_axis</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>Q10_text</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Q10_axis</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Q11_text</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>Q11_axis</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Q12</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>Q12_text</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>Q12_axis</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>Q13</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>Q13_text</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>Q13_axis</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>Q14</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>Q14_text</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>Q14_axis</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>Q15</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>Q15_text</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Q15_axis</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Q16</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>Q16_text</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>Q16_axis</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>Q17</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>Q17_text</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>Q17_axis</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>Q18</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>Q18_text</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>Q18_axis</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>Q19</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>Q19_text</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>Q19_axis</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>Q20_text</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>Q20_axis</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>Q21</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>Q21_text</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>Q21_axis</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>Q22</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>Q22_text</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>Q22_axis</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>Q23</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>Q23_text</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>Q23_axis</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>Q24</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>Q24_text</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>Q24_axis</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>Q25</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>Q25_text</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>Q25_axis</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>Q26</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>Q26_text</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>Q26_axis</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>Q27</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>Q27_text</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>Q27_axis</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>Q28</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>Q28_text</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>Q28_axis</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>Q29</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>Q29_text</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>Q29_axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>14015</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>حنا سامر نايف المدانات</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>بنين / جبل عمان</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>أخرى</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>yyy</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>hh</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>hh</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="N2" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-03-25 09:35:10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>المحور الأول: البيئة المدرسية</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>88</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>المحور الثاني: التحصيل الأكاديمي</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V2" t="n">
+        <v>76</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>المحور الثالث: الكادر التعليمي</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>88</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>المحور الرابع: التواصل</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>88</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>المحور الخامس: الرضا العام</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>92</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>المحور السادس: النقل المدرسي</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>هل البيئة المدرسية مناسبة لطلاب المرحلة؟</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>المحور الأول: البيئة المدرسية</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>هل الانضباط المدرسي جيد داخل المدرسة؟</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>المحور الأول: البيئة المدرسية</t>
+        </is>
+      </c>
+      <c r="AO2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>هل تشعر أن مرافق المدرسة مناسبة؟</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>المحور الأول: البيئة المدرسية</t>
+        </is>
+      </c>
+      <c r="AR2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>هل مستوى النظافة في المدرسة جيد؟</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>المحور الأول: البيئة المدرسية</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>هل الأجواء العامة مشجعة للتعلم؟</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>المحور الأول: البيئة المدرسية</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>هل المنهاج مناسب لمستوى الطالب؟</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>المحور الثاني: التحصيل الأكاديمي</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>هل الشرح داخل الصف واضح؟</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>المحور الثاني: التحصيل الأكاديمي</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>هل يتم متابعة الواجبات بشكل مناسب؟</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>المحور الثاني: التحصيل الأكاديمي</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>هل يتم إعلامكم بمستوى الطالب باستمرار؟</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>المحور الثاني: التحصيل الأكاديمي</t>
+        </is>
+      </c>
+      <c r="BJ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>هل يوجد تحسن في أداء الطالب؟</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>المحور الثاني: التحصيل الأكاديمي</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>هل المعلمون ملتزمون بواجباتهم؟</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>المحور الثالث: الكادر التعليمي</t>
+        </is>
+      </c>
+      <c r="BP2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>هل يتعامل المعلمون باحترام مع الطلبة؟</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>المحور الثالث: الكادر التعليمي</t>
+        </is>
+      </c>
+      <c r="BS2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>هل يوجد تعاون جيد بين المعلمين وأولياء الأمور؟</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>المحور الثالث: الكادر التعليمي</t>
+        </is>
+      </c>
+      <c r="BV2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>هل يتم مراعاة الفروق الفردية؟</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>المحور الثالث: الكادر التعليمي</t>
+        </is>
+      </c>
+      <c r="BY2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>هل يتم توجيه الطالب أكاديميًا بشكل مناسب؟</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>المحور الثالث: الكادر التعليمي</t>
+        </is>
+      </c>
+      <c r="CB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>هل المدرسة تتواصل معكم عند الحاجة؟</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>المحور الرابع: التواصل</t>
+        </is>
+      </c>
+      <c r="CE2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>هل يتم الرد على استفساراتكم بسرعة؟</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>المحور الرابع: التواصل</t>
+        </is>
+      </c>
+      <c r="CH2" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>هل قنوات التواصل واضحة؟</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>المحور الرابع: التواصل</t>
+        </is>
+      </c>
+      <c r="CK2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>هل يتم تزويدكم بالملاحظات الأكاديمية بانتظام؟</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>المحور الرابع: التواصل</t>
+        </is>
+      </c>
+      <c r="CN2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>هل تشعر أن رأيك مهم بالنسبة للمدرسة؟</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>المحور الرابع: التواصل</t>
+        </is>
+      </c>
+      <c r="CQ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>هل أنت راضٍ عن المدرسة بشكل عام؟</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>المحور الخامس: الرضا العام</t>
+        </is>
+      </c>
+      <c r="CT2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>هل توصي بهذه المدرسة للآخرين؟</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>المحور الخامس: الرضا العام</t>
+        </is>
+      </c>
+      <c r="CW2" t="n">
+        <v>5</v>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>هل ترى أن المدرسة تلبي احتياجات الطالب؟</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>المحور الخامس: الرضا العام</t>
+        </is>
+      </c>
+      <c r="CZ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>هل ترغب باستمرار ابنك/ابنتك فيها؟</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>المحور الخامس: الرضا العام</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>4</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>هل مستوى الإدارة المدرسية مرضٍ؟</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>المحور الخامس: الرضا العام</t>
+        </is>
+      </c>
+      <c r="DF2" t="n">
+        <v>5</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>التزام السائق بالدقة الزمنية لحضور الحافلة إلى المنزل</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>المحور السادس: النقل المدرسي</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>5</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>سلوك السائق مع الطلبة</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>المحور السادس: النقل المدرسي</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>4</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>اهتمام المرافقة بالطلبة أثناء الجولة</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>المحور السادس: النقل المدرسي</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>4</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>شعورك بأمان الطالب/الطالبة أثناء استخدام الحافلة</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>المحور السادس: النقل المدرسي</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
